--- a/attention/mixed_quant_sparse_flash_mla/tests/pytest/excel/example.xlsx
+++ b/attention/mixed_quant_sparse_flash_mla/tests/pytest/excel/example.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="decode" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="prefill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="test_cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,630 +428,1320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Testcase_Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>layout_q</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>layout_kv</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>q_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ori_kv_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>cmp_kv_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>block_size1</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>block_size2</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>softmax_scale</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cmp_ratio</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ori_mask_mode</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>cmp_mask_mode</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ori_win_left</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ori_win_right</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>kv_quant_mode</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tile_size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>rope_head_dim</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>template_run_mode</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>actlen_mode</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>S1EQS2</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>topk_value_mode</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>return_softmax_lse</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SWA_decode_TND_BF16_FP8</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>TND</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>PA_ND</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>torch.bfloat16</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>torch.float8_e4m3fn</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>torch.float8_e4m3fn</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>8193</v>
       </c>
-      <c r="J2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="J2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="M2" t="n">
-        <v>512</v>
-      </c>
-      <c r="N2" t="n">
-        <v>128</v>
-      </c>
-      <c r="O2" t="n">
-        <v>128</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>0.04419417</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="Q2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>64</v>
-      </c>
-      <c r="X2" t="n">
-        <v>64</v>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>SWA</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="AA2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SWA_prefill_TND_BF16_FP8</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>TND</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>PA_ND</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>torch.bfloat16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CFA_decode_TND_BF16_FP8_ratio4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CFA_prefill_TND_BF16_FP8_ratio4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SCFA_decode_TND_BF16_FP8_K512_ratio4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>SCFA</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SCFA_prefill_TND_BF16_FP8_K512_ratio4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>SCFA</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CFA_decode_TND_BF16_FP8_ratio128</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SCFA_decode_TND_BF16_FP8_K1024_ratio4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>SCFA</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SWA_decode_TND_BF16_HIF8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>torch.uint8</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>torch.uint8</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>8193</v>
       </c>
-      <c r="J3" t="n">
-        <v>64</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="J10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CFA_decode_TND_BF16_HIF8_ratio4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PA_ND</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>torch.uint8</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>torch.uint8</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="N3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O3" t="n">
-        <v>128</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>0.04419417</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="Q11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="S3" t="n">
+      <c r="R11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T11" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="W3" t="n">
-        <v>64</v>
-      </c>
-      <c r="X3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>SWA</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="W11" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="AA11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Testcase_Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>layout_q</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>layout_kv</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>q_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ori_kv_type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cmp_kv_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>N1</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>N2</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>block_size1</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>block_size2</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>softmax_scale</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>cmp_ratio</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ori_mask_mode</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>cmp_mask_mode</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ori_win_left</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>ori_win_right</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>kv_quant_mode</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>tile_size</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>rope_head_dim</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>template_run_mode</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>actlen_mode</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>S1EQS2</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>topk_value_mode</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>return_softmax_lse</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SCFA_decode_TND_BF16_HIF8_K512_ratio4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>TND</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>PA_ND</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>torch.bfloat16</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>torch.float8_e4m3fn</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>torch.float8_e4m3fn</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8192</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8192</v>
-      </c>
-      <c r="J2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>torch.uint8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>torch.uint8</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>8193</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M12" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="N2" t="n">
-        <v>128</v>
-      </c>
-      <c r="O2" t="n">
-        <v>128</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N12" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="P12" s="2" t="n">
         <v>0.04419417</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="R12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T12" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>64</v>
-      </c>
-      <c r="X2" t="n">
-        <v>64</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>SWA</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>SCFA</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+      <c r="AA12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
